--- a/artfynd/A 55210-2021 artfynd.xlsx
+++ b/artfynd/A 55210-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55210-2021 artfynd.xlsx
+++ b/artfynd/A 55210-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>74916450</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412835.4619377084</v>
+        <v>412835</v>
       </c>
       <c r="R2" t="n">
-        <v>6584882.441505092</v>
+        <v>6584882</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2018-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117096034</v>
+        <v>115401809</v>
       </c>
       <c r="B3" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,36 +800,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>I2 Skogen Våxnäs, I2-skogen, Vrm</t>
+          <t>S Sanna Karlstad, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412627</v>
+        <v>412841</v>
       </c>
       <c r="R3" t="n">
-        <v>6584753</v>
+        <v>6584902</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,27 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett ex observerades på tallträdstam sannolikt födosökande</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +867,358 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Claes Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Claes Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117096034</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>I2 Skogen Våxnäs, I2-skogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412627</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6584753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett ex observerades på tallträdstam sannolikt födosökande</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Bo Svärd</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Bo Svärd</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74916419</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karlstad I2-området, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412541</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6584768</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110752192</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Sanna Karlstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412841</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584902</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Claes Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Claes Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55210-2021 artfynd.xlsx
+++ b/artfynd/A 55210-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74916450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115401809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117096034</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74916419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,8 +1244,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110752192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>